--- a/public/templates/قالب-دورة-إدارة-الأنقاض.xlsx
+++ b/public/templates/قالب-دورة-إدارة-الأنقاض.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,10 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,6 +522,26 @@
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>صور قبل التنفيذ (روابط)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>صور أثناء التنفيذ (روابط)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>صور بعد الإنجاز (روابط)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>رابط مجلد الصور والوثائق</t>
         </is>
       </c>
     </row>
@@ -537,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -616,6 +640,30 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>روابط الصور</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>رابط أو أكثر لكل صورة (يفصل بينها فاصلة أو سطر جديد) من مستودع الملفات المعتمد: Google Drive أو OneDrive أو خادم الوزارة. تظهر تلقائياً في معرض المشروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>رابط مجلد الصور والوثائق</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>رابط المجلد الكامل للمشروع في مستودع الملفات، يظهر زراً «فتح المجلد» في بطاقة المشروع والأرشيف.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
